--- a/deney_sonuclari.xlsx
+++ b/deney_sonuclari.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,16 +485,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -502,16 +502,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6454.22602930529</v>
+        <v>6559.947274597637</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3070.306943494167</v>
       </c>
       <c r="I2" t="n">
-        <v>6414.680422393714</v>
+        <v>6489.662912755876</v>
       </c>
       <c r="J2" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3">
@@ -519,33 +519,33 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>0.224</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>(-5, -2, -8)</t>
+          <t>(-2, -3, -10)</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>6506.302096540609</v>
+        <v>6619.010017782988</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3866.966394413575</v>
       </c>
       <c r="I3" t="n">
-        <v>6364.529874562091</v>
+        <v>6487.295585877361</v>
       </c>
       <c r="J3" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4">
@@ -553,33 +553,611 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
+        <v>50</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>(-2, -3, -10)</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>6500.174860685177</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2437.893175783309</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6425.332423069976</v>
+      </c>
+      <c r="J4" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>250</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>(-2, -3, -10)</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>6578.320984858237</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2796.291580903666</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6386.397803906513</v>
+      </c>
+      <c r="J5" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>(-2, -3, -10)</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>6521.216494309801</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2746.642922425909</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6420.497260921495</v>
+      </c>
+      <c r="J6" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>(-2, -3, -10)</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>6544.823583429961</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2702.456466002863</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6387.742006132348</v>
+      </c>
+      <c r="J7" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>(-2, -3, -10)</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>6458.775236846582</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3033.669688958004</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6387.631434467853</v>
+      </c>
+      <c r="J8" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>(-3, -5, -7)</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>6475.894888900173</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>6416.633069728103</v>
-      </c>
-      <c r="J4" t="n">
-        <v>280</v>
+      <c r="B9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C9" t="n">
+        <v>250</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>(-2, -3, -10)</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>6475.685867276548</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2981.448135164262</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6376.867673854595</v>
+      </c>
+      <c r="J9" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>(-2, -3, -10)</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>6552.256024811833</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3121.721089042695</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6489.150481289913</v>
+      </c>
+      <c r="J10" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>(-2, -3, -10)</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>6507.590512633428</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2685.72025771476</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6431.082271783714</v>
+      </c>
+      <c r="J11" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>(-2, -3, -10)</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>6441.585181407591</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2423.916726941415</v>
+      </c>
+      <c r="I12" t="n">
+        <v>6400.633562856772</v>
+      </c>
+      <c r="J12" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C13" t="n">
+        <v>250</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>(-2, -3, -10)</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>6532.643887955759</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3532.971162269885</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6369.463356619326</v>
+      </c>
+      <c r="J13" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>20</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>(-2, -3, -10)</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>6512.198442554151</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3502.412982365294</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6414.338490531177</v>
+      </c>
+      <c r="J14" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>20</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>(-2, -3, -10)</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>6475.92126643194</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3317.127729207668</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6313.39862550131</v>
+      </c>
+      <c r="J15" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>20</v>
+      </c>
+      <c r="C16" t="n">
+        <v>50</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>(-2, -3, -10)</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>6428.187179797362</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2459.3753095794</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6370.916273847028</v>
+      </c>
+      <c r="J16" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C17" t="n">
+        <v>250</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>(-2, -3, -10)</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>6447.059909242368</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3033.370609668136</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6345.22404037485</v>
+      </c>
+      <c r="J17" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>50</v>
+      </c>
+      <c r="C18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>(-2, -3, -10)</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>6481.331417914989</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2692.393754816384</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6403.930015188119</v>
+      </c>
+      <c r="J18" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>50</v>
+      </c>
+      <c r="C19" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>(-2, -3, -10)</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>6454.367817797877</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3796.006946188617</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6368.73675928257</v>
+      </c>
+      <c r="J19" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>50</v>
+      </c>
+      <c r="C20" t="n">
+        <v>50</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>(-2, -3, -10)</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>6438.341161573552</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2580.097030184859</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6321.732968219828</v>
+      </c>
+      <c r="J20" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>50</v>
+      </c>
+      <c r="C21" t="n">
+        <v>250</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>(-2, -3, -10)</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>6449.463278305614</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2876.764332303361</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6355.765432845352</v>
+      </c>
+      <c r="J21" t="n">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
